--- a/data-sources/upcoming_events.xlsx
+++ b/data-sources/upcoming_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal Projects\gsb-community\data-sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CA4AF9-A6EC-4144-923A-0C1DA834A671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01796B1-BD90-4C1A-A531-994C87BC3343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>event_id</t>
   </si>
@@ -209,6 +209,33 @@
   </si>
   <si>
     <t>All temples</t>
+  </si>
+  <si>
+    <t>Diwali</t>
+  </si>
+  <si>
+    <t>Dipavali, commonly known as Diwali, is the Hindu festival of lights, with variations celebrated in other Indian religions such as Jainism and Sikhism. It is associated with the spiritual victory or triumph of Dharma over Adharma, light over darkness, good over evil, and knowledge over ignorance.</t>
+  </si>
+  <si>
+    <t>Abhiseka and Aarathi at Karanakodam Tirumala Dewaswom, SVB Devi Temple, Sahasra Deepalankara Seva</t>
+  </si>
+  <si>
+    <t>Venkatachalapathy Aarattu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venkatachalapathy Aarattu of 2026 a 5 days festival from 18th December 2026 and concludes on 22nd December 2026, Kodiyeetam on 18th December and Aarattu on 22nd December 2026. </t>
+  </si>
+  <si>
+    <t>Karanakodam Tirumala Dewaswam</t>
+  </si>
+  <si>
+    <t>SVB Devi Devi temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thulasi Pooja </t>
+  </si>
+  <si>
+    <t>Tulsi Pooja is a sacred Hindu ritual dedicated to worshipping the holy basil plant (Tulsi), which is revered as an earthly incarnation of Goddess Lakshmi and the consort of Lord</t>
   </si>
 </sst>
 </file>
@@ -269,10 +296,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -280,8 +305,25 @@
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,13 +658,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="53.77734375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -632,139 +674,139 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+    <row r="6" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <v>46279</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -773,40 +815,155 @@
       <c r="C7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <v>46269</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="10">
         <v>46315</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>0.25</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46334</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="9">
+        <v>46374</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="9">
+        <v>46378</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="9">
+        <v>46343</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="9">
+        <v>46346</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
